--- a/eagle/testmaster/Book11.xlsx
+++ b/eagle/testmaster/Book11.xlsx
@@ -214,12 +214,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -234,8 +240,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,107 +551,107 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
         <v>60</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H6" t="s">
@@ -652,124 +659,124 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" t="s">
+      <c r="E17" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" t="s">
+      <c r="E18" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" t="s">
+      <c r="E19" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="22" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" t="s">
+      <c r="E22" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="23" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" t="s">
+      <c r="E23" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" t="s">
+      <c r="E24" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" t="s">
+      <c r="E25" s="1" t="s">
         <v>57</v>
       </c>
     </row>
